--- a/Output/27072026_Taux_Noemie 2.xlsx
+++ b/Output/27072026_Taux_Noemie 2.xlsx
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,35 +109,35 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,7 +726,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1762,540 +1766,476 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
+          <t>Actifs2</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Non actifs2</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Non_Noémisable2</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Taux</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Offres</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Individuel ou Collectif</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>ordre</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Client / Offre</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Actifs</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>non Actifs</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Non_noémisable</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Taux de noémisation</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Individuel ou Collectif</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="9" t="n">
+        <v>0.8931297709923665</v>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>NUANCE</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>NUANCE</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="n">
-        <v>234</v>
-      </c>
-      <c r="D2" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>0.8931297709923665</v>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="9" t="n">
+        <v>0.8638171852899575</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>PSC SANTE MEAE</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="G3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>PSC SANTE MEAE</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="n">
-        <v>19543</v>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>2132</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>949</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0.8638171852899575</v>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n">
+        <v>0.8359468077650851</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Education Jeunesse Sports Enseignement Supérieur Recherche</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="G4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Education Jeunesse Sports Enseignement Supérieur Recherche</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>1526800</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>154224</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>145408</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>0.8359468077650851</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="9" t="n">
+        <v>0.8434630520332314</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>La juridiction administrative</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="G5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>La juridiction administrative</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>3858</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>360</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>356</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>0.8434630520332314</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="9" t="n">
+        <v>0.83796658371845</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>PSC SANTE MINISTERE DE LA CULTURE</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="G6" s="11" t="n">
         <v>5</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>PSC SANTE MINISTERE DE LA CULTURE</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>23572</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>1818</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>2740</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0.83796658371845</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.9750039301996541</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>MAEE PR+MAEE SANTE RETRAITE + MAEE PNR</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="n">
         <v>6</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>MAEE PR+MAEE SANTE RETRAITE + MAEE PNR</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>6202</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>147</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>0.9750039301996541</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
+        <v>1114038</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>31661</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>4527</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.9685383568098791</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>MSP RETRAITES+MGEN SANTE</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>MSP RETRAITES+MGEN SANTE</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>1114038</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>31661</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>4527</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0.9685383568098791</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="9" t="n">
+        <v>0.949483306836248</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>MGEN ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="n">
         <v>8</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>MGEN ALTERNATIVE</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>23889</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>1216</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>0.949483306836248</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
+        <v>6682</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>538</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.9159698423577793</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>MTE ACTIF + MTE</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="n">
         <v>9</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>MTE ACTIF + MTE</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>6682</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>538</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0.9159698423577793</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
+        <v>99797</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>11820</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>515</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.8899957193307887</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>EFS SANTE + EFS SANTE BRED</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>EFS SANTE + EFS SANTE BRED</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>99797</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>11820</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>515</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0.8899957193307887</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="9" t="n">
+        <v>0.7687276317413304</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>MGEN OJI</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>11</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>MGEN OJI</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>24916</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>6653</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>843</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>0.7687276317413304</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
+        <v>6851</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>3535</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>6778</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.3991493824283384</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>MISP ACTIF + MISP + MISP R</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="n">
         <v>12</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>MISP ACTIF + MISP + MISP R</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>6851</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>3535</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>6778</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>0.3991493824283384</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
+        <v>11379</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>8853</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>16342</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.3111226554382895</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>C2S PF + C2S</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>C2S PF + C2S</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>11379</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>8853</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>16342</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>0.3111226554382895</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="9" t="n">
+        <v>0.837863167760075</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>C2S SORTIE</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>C2S SORTIE</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>894</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>165</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>0.837863167760075</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>PSC SANTE MIOM</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>526</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>PSC SANTE MSST</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="n"/>
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="A19" s="12" t="n">
+        <v>2868655</v>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>223687</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>178619</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>0.8770067879133991</v>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>2868655</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>223687</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>178619</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>0.8770067879133991</v>
-      </c>
     </row>
     <row r="20">
-      <c r="B20" s="15" t="inlineStr">
+      <c r="A20" s="15" t="n">
+        <v>1574007</v>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>158554</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>149461</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>0.8363382574698914</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Total Collectif</t>
         </is>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>1574007</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>158554</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>149461</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>0.8363382574698914</v>
-      </c>
     </row>
     <row r="21">
-      <c r="B21" s="15" t="inlineStr">
+      <c r="A21" s="15" t="n">
+        <v>1294648</v>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>65133</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>29158</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>0.9321129293655085</v>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>Total Individuel</t>
         </is>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>1294648</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>65133</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>29158</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>0.9321129293655085</v>
       </c>
     </row>
   </sheetData>

--- a/Output/27072026_Taux_Noemie 2.xlsx
+++ b/Output/27072026_Taux_Noemie 2.xlsx
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +68,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -104,35 +109,35 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1762,540 +1767,476 @@
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
+          <t>Actifs2</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Non actifs2</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Non_noémisable2</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Taux</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Offres</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Individuel ou Collectif</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
           <t>ordre</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>Client / Offre</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Actifs</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>non Actifs</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Non_noémisable</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Taux de noémisation</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Individuel ou Collectif</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="n">
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="9" t="n">
+        <v>0.8931297709923665</v>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>NUANCE</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>NUANCE</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="n">
-        <v>234</v>
-      </c>
-      <c r="D2" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" s="11" t="n">
-        <v>0.8931297709923665</v>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="9" t="n">
+        <v>0.8638171852899575</v>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>PSC SANTE MEAE</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
+      <c r="G3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>PSC SANTE MEAE</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="n">
-        <v>19543</v>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>2132</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>949</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>0.8638171852899575</v>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="9" t="n">
+        <v>0.8359468077650851</v>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Education Jeunesse Sports Enseignement Supérieur Recherche</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="n">
+      <c r="G4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Education Jeunesse Sports Enseignement Supérieur Recherche</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>1526800</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>154224</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>145408</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>0.8359468077650851</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="9" t="n">
+        <v>0.8434630520332314</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>La juridiction administrative</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="G5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>La juridiction administrative</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>3858</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>360</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>356</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>0.8434630520332314</v>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="9" t="n">
+        <v>0.83796658371845</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>PSC SANTE MINISTERE DE LA CULTURE</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="G6" s="11" t="n">
         <v>5</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>PSC SANTE MINISTERE DE LA CULTURE</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>23572</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>1818</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>2740</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>0.83796658371845</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>147</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.9750039301996541</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>MAEE PR+MAEE SANTE RETRAITE + MAEE PNR</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="n">
         <v>6</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>MAEE PR+MAEE SANTE RETRAITE + MAEE PNR</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>6202</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>147</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>0.9750039301996541</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
+        <v>1114038</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>31661</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>4527</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.9685383568098791</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>MSP RETRAITES+MGEN SANTE</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>MSP RETRAITES+MGEN SANTE</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>1114038</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>31661</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>4527</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0.9685383568098791</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="9" t="n">
+        <v>0.949483306836248</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>MGEN ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="n">
         <v>8</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>MGEN ALTERNATIVE</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>23889</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>1216</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>0.949483306836248</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
+        <v>6682</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>538</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.9159698423577793</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>MTE ACTIF + MTE</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="n">
         <v>9</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>MTE ACTIF + MTE</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>6682</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>538</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>75</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0.9159698423577793</v>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="n">
+        <v>99797</v>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>11820</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>515</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.8899957193307887</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>EFS SANTE + EFS SANTE BRED</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>EFS SANTE + EFS SANTE BRED</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>99797</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>11820</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>515</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0.8899957193307887</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="9" t="n">
+        <v>0.7687276317413304</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>MGEN OJI</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>11</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>MGEN OJI</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>24916</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>6653</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>843</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>0.7687276317413304</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="n">
+        <v>6851</v>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>3535</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>6778</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.3991493824283384</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>MISP ACTIF + MISP + MISP R</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="n">
         <v>12</v>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>MISP ACTIF + MISP + MISP R</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
-        <v>6851</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>3535</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>6778</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>0.3991493824283384</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
+        <v>11379</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>8853</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>16342</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.3111226554382895</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>C2S PF + C2S</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>C2S PF + C2S</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>11379</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>8853</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>16342</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>0.3111226554382895</v>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="9" t="n">
+        <v>0.837863167760075</v>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>C2S SORTIE</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>C2S SORTIE</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>894</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>165</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>0.837863167760075</v>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>PSC SANTE MIOM</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>526</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>PSC SANTE MSST</t>
         </is>
       </c>
-      <c r="C17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="n"/>
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="A19" s="12" t="n">
+        <v>2868655</v>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>223687</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>178619</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>0.8770067879133991</v>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>2868655</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>223687</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>178619</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>0.8770067879133991</v>
-      </c>
     </row>
     <row r="20">
-      <c r="B20" s="15" t="inlineStr">
+      <c r="A20" s="15" t="n">
+        <v>1574007</v>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>159099</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>149464</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>0.8360948065676177</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Total Collectif</t>
         </is>
       </c>
-      <c r="C20" s="16" t="n">
-        <v>1574007</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>158554</v>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>149461</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>0.8363382574698914</v>
-      </c>
     </row>
     <row r="21">
-      <c r="B21" s="15" t="inlineStr">
+      <c r="A21" s="15" t="n">
+        <v>1294648</v>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>64588</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>29155</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>0.9324808357299925</v>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>Total Individuel</t>
         </is>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>1294648</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>65133</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>29158</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>0.9321129293655085</v>
       </c>
     </row>
   </sheetData>
